--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -419,6 +419,23 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>2026-02-19 11:47:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:27:05</t>
         </is>
       </c>
     </row>
@@ -683,13 +700,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E2D3D11-3789-428C-89E4-60021E5080D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13A4FD71-B37F-456A-AE88-1DAE0EA9F817}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4B53037-D293-4797-8EC7-AE2F089A049B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC2F6531-8991-4EF1-B5FD-02938A64FDD3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0262BBF7-7C5E-43E5-B11A-B7A6A5D83CAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B90CB467-6C5A-4122-A080-C4EB558C3D2A}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -436,6 +436,40 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>2026-02-23 11:27:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-02-24 15:22:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:15:34</t>
         </is>
       </c>
     </row>
@@ -700,13 +734,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13A4FD71-B37F-456A-AE88-1DAE0EA9F817}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45CFDEC3-A1A7-49EB-9FB6-F7C16EFB765E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC2F6531-8991-4EF1-B5FD-02938A64FDD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF03338-996D-4081-9BE1-83A5DEE77CC6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B90CB467-6C5A-4122-A080-C4EB558C3D2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE22F1CB-2E0B-4D9B-8219-06F2063522A5}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -470,6 +470,108 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>2026-02-24 16:15:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:25:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-02-27 12:39:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-12 10:10:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-03-16 13:48:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-03-17 12:26:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-03-17 14:16:09</t>
         </is>
       </c>
     </row>
@@ -734,13 +836,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45CFDEC3-A1A7-49EB-9FB6-F7C16EFB765E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F9AEAE-59AF-4164-A0E3-BDDC82A1B9CD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF03338-996D-4081-9BE1-83A5DEE77CC6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7DB758E-5B44-486B-B008-4CB27808D5AC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE22F1CB-2E0B-4D9B-8219-06F2063522A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76182163-0965-4940-8296-3ED71B0BCAE3}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -572,6 +572,40 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>2026-03-17 14:16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-03-18 11:51:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-03-18 15:11:14</t>
         </is>
       </c>
     </row>
@@ -836,13 +870,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F9AEAE-59AF-4164-A0E3-BDDC82A1B9CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49B25287-3537-4478-8F7F-0F03F31C8E6C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7DB758E-5B44-486B-B008-4CB27808D5AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2650F916-D7A1-46EE-A252-4CF2A02E91A7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76182163-0965-4940-8296-3ED71B0BCAE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30858FF9-2DB6-4AD6-9F06-EFA84B5A2C59}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -606,6 +606,40 @@
       <c r="C15" t="inlineStr">
         <is>
           <t>2026-03-18 15:11:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-03-19 14:03:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-03-19 14:20:30</t>
         </is>
       </c>
     </row>
@@ -870,13 +904,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49B25287-3537-4478-8F7F-0F03F31C8E6C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCE9CECD-6B82-46B1-92A1-9CE773CCA2F5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2650F916-D7A1-46EE-A252-4CF2A02E91A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6D8C8AD-1B56-488A-B60F-B98CA70300CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30858FF9-2DB6-4AD6-9F06-EFA84B5A2C59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A2A925D-DDD1-45EA-AF54-F15AA80C8379}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -640,6 +640,57 @@
       <c r="C17" t="inlineStr">
         <is>
           <t>2026-03-19 14:20:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-03-20 11:30:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:28:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:37:25</t>
         </is>
       </c>
     </row>
@@ -904,13 +955,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCE9CECD-6B82-46B1-92A1-9CE773CCA2F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DACD6FB-C686-417D-A8B1-50AEF392D0E3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6D8C8AD-1B56-488A-B60F-B98CA70300CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20A8CCBE-0636-46B6-969A-000D58572033}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A2A925D-DDD1-45EA-AF54-F15AA80C8379}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AA6BB59-FD1A-45B3-8899-746BAF81E399}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -691,6 +691,40 @@
       <c r="C20" t="inlineStr">
         <is>
           <t>2026-03-24 10:37:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:55:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-03-30 15:28:23</t>
         </is>
       </c>
     </row>
@@ -955,13 +989,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DACD6FB-C686-417D-A8B1-50AEF392D0E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D65252D2-A329-4C09-9E3E-71A67B6AF888}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20A8CCBE-0636-46B6-969A-000D58572033}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBD395C4-E3A9-4D97-A3D6-CB2452901292}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AA6BB59-FD1A-45B3-8899-746BAF81E399}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B46AF2B-6471-4715-AA42-D3626BAB0B03}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -725,6 +725,57 @@
       <c r="C22" t="inlineStr">
         <is>
           <t>2026-03-30 15:28:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:45:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-04-09 11:08:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-04-09 16:18:50</t>
         </is>
       </c>
     </row>
@@ -989,13 +1040,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D65252D2-A329-4C09-9E3E-71A67B6AF888}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30DEC44A-F242-42D7-9154-45CD6CEAB484}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBD395C4-E3A9-4D97-A3D6-CB2452901292}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEF77AA3-4277-4250-B3B9-315D48F5646C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B46AF2B-6471-4715-AA42-D3626BAB0B03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6457D91E-3C05-4F17-9051-0397E1F5BE58}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -776,6 +776,74 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>2026-04-09 16:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:26:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:26:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-04-14 09:26:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:06:06</t>
         </is>
       </c>
     </row>
@@ -1040,13 +1108,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30DEC44A-F242-42D7-9154-45CD6CEAB484}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E8D7EF4-F7AD-4668-AB83-AC3ACDBE21A3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEF77AA3-4277-4250-B3B9-315D48F5646C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2772E074-CC26-4870-996D-3F22D711DC20}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6457D91E-3C05-4F17-9051-0397E1F5BE58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68A3AE0A-BB35-4AC3-90A7-61580277AFFD}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -844,6 +844,57 @@
       <c r="C29" t="inlineStr">
         <is>
           <t>2026-04-15 11:06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:21:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-04-16 09:45:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:21:29</t>
         </is>
       </c>
     </row>
@@ -1108,13 +1159,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E8D7EF4-F7AD-4668-AB83-AC3ACDBE21A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A5DA93F-8B64-4C25-85FB-BFB34D700397}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2772E074-CC26-4870-996D-3F22D711DC20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B94FB21F-4D69-46DF-81F1-3B30EF5C181C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68A3AE0A-BB35-4AC3-90A7-61580277AFFD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{895A2B9E-620C-4DD5-9D70-61A26072FEFB}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -895,6 +895,40 @@
       <c r="C32" t="inlineStr">
         <is>
           <t>2026-04-17 10:21:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-04-20 10:07:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-04-21 09:55:48</t>
         </is>
       </c>
     </row>
@@ -1159,13 +1193,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A5DA93F-8B64-4C25-85FB-BFB34D700397}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C168C831-AFAB-4CD0-98E8-0266DAD6668D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B94FB21F-4D69-46DF-81F1-3B30EF5C181C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30962EE3-5E68-4682-966F-8026FA6C05DF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{895A2B9E-620C-4DD5-9D70-61A26072FEFB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2A099F0-23CC-4342-97FA-7DF1EF9B01A2}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -929,6 +929,57 @@
       <c r="C34" t="inlineStr">
         <is>
           <t>2026-04-21 09:55:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-04-23 10:20:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-04-23 14:34:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-04-23 14:52:50</t>
         </is>
       </c>
     </row>
@@ -1193,13 +1244,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C168C831-AFAB-4CD0-98E8-0266DAD6668D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95318E3B-2482-42F2-99FF-14E889686836}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30962EE3-5E68-4682-966F-8026FA6C05DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B50BF38B-926D-4F8D-A0CD-B1BA04D85A68}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2A099F0-23CC-4342-97FA-7DF1EF9B01A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5559005-973C-447D-ADF7-DA9E2F709660}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -980,6 +980,40 @@
       <c r="C37" t="inlineStr">
         <is>
           <t>2026-04-23 14:52:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-04-27 14:48:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:41:14</t>
         </is>
       </c>
     </row>
@@ -1244,13 +1278,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95318E3B-2482-42F2-99FF-14E889686836}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02996B80-3846-410F-AB41-8AB935EEFB55}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B50BF38B-926D-4F8D-A0CD-B1BA04D85A68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B91477-704C-4F02-8C96-75E69CFCD842}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5559005-973C-447D-ADF7-DA9E2F709660}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA97A402-2DF9-4365-8542-AC9011575AD6}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1017,274 +1017,41 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-05-04 08:47:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-05-04 11:42:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02996B80-3846-410F-AB41-8AB935EEFB55}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B91477-704C-4F02-8C96-75E69CFCD842}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA97A402-2DF9-4365-8542-AC9011575AD6}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1051,7 +1051,325 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-05-04 12:07:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:08:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-05-04 15:14:12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B50FFAA0-BF32-4B02-A8C9-1F12CC3820EB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BEAD04B-F8AC-4BFF-A769-3106FA942205}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA40003-DC01-45A0-B5DD-731FF1301B70}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1099,6 +1099,23 @@
       <c r="C44" t="inlineStr">
         <is>
           <t>2026-05-04 15:14:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:24:36</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1380,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B50FFAA0-BF32-4B02-A8C9-1F12CC3820EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52140036-20E7-4809-AA74-D7C37B640178}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BEAD04B-F8AC-4BFF-A769-3106FA942205}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F343353A-8CFA-4CC3-A15C-E4AB7FB681BE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA40003-DC01-45A0-B5DD-731FF1301B70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60242F9E-5C3E-4BA8-81CF-095B1AC5914A}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1119,274 +1119,109 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-05-13 09:00:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-05-13 09:38:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-05-13 09:39:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:19:45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52140036-20E7-4809-AA74-D7C37B640178}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F343353A-8CFA-4CC3-A15C-E4AB7FB681BE}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60242F9E-5C3E-4BA8-81CF-095B1AC5914A}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1221,7 +1221,308 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-05-14 10:43:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-05-14 10:46:16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCDBEC4B-284D-4156-A417-C6237787F552}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6896394-573B-4046-AED7-AF6D75229C62}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DAB4F60-4563-45F8-BC66-96503307189D}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1252,6 +1252,23 @@
       <c r="C53" t="inlineStr">
         <is>
           <t>2026-05-14 10:46:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:22:24</t>
         </is>
       </c>
     </row>
@@ -1516,13 +1533,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCDBEC4B-284D-4156-A417-C6237787F552}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80530B0-E970-4CA5-992C-13673EB25103}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6896394-573B-4046-AED7-AF6D75229C62}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACB20C09-615F-4533-AE48-B92083E80422}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DAB4F60-4563-45F8-BC66-96503307189D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BBA9067-BF8F-45F4-A06A-B0AAD20F6929}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1269,6 +1269,125 @@
       <c r="C54" t="inlineStr">
         <is>
           <t>2026-05-22 10:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-06-02 08:30:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-06-02 08:50:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:06:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:33:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:44:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-06-02 13:41:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-06-02 13:51:42</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80530B0-E970-4CA5-992C-13673EB25103}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A703F0F-A1C5-4235-8781-183E8F38AE6E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACB20C09-615F-4533-AE48-B92083E80422}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8149EB11-049B-4914-A65B-C7A3687BF205}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BBA9067-BF8F-45F4-A06A-B0AAD20F6929}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{124962BC-00C9-44B3-8C01-00BF1C0F7B33}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1388,6 +1388,74 @@
       <c r="C61" t="inlineStr">
         <is>
           <t>2026-06-02 13:51:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:15:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-06-08 10:42:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-06-09 08:21:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-06-09 14:41:28</t>
         </is>
       </c>
     </row>
@@ -1652,13 +1720,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A703F0F-A1C5-4235-8781-183E8F38AE6E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E100B9C4-D843-48E5-8E55-A80132DE65AF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8149EB11-049B-4914-A65B-C7A3687BF205}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1AA107C-545C-4FA1-80D4-A3A1B5806596}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{124962BC-00C9-44B3-8C01-00BF1C0F7B33}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3B4D13F-841C-45D6-98B6-5F3D816109BF}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1456,6 +1456,57 @@
       <c r="C65" t="inlineStr">
         <is>
           <t>2026-06-09 14:41:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-06-09 15:07:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-06-09 15:15:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-06-09 15:25:00</t>
         </is>
       </c>
     </row>
@@ -1720,13 +1771,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E100B9C4-D843-48E5-8E55-A80132DE65AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F400D90F-2083-4E68-BEC1-A8CB42C95161}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1AA107C-545C-4FA1-80D4-A3A1B5806596}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5FD4E9C-E3A7-4A25-A09D-C85D02CB3EC4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3B4D13F-841C-45D6-98B6-5F3D816109BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6905357B-2D29-4AA6-B6A6-D1C51E7B2038}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1507,6 +1507,23 @@
       <c r="C68" t="inlineStr">
         <is>
           <t>2026-06-09 15:25:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:24:28</t>
         </is>
       </c>
     </row>
@@ -1771,13 +1788,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F400D90F-2083-4E68-BEC1-A8CB42C95161}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34BD3469-273E-43BC-BFDF-29D157941C03}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5FD4E9C-E3A7-4A25-A09D-C85D02CB3EC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBFA5618-94B5-4093-B3EF-6CE6388D6FBF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6905357B-2D29-4AA6-B6A6-D1C51E7B2038}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78961B9D-F687-4FE1-8410-2302833B4197}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1524,6 +1524,23 @@
       <c r="C69" t="inlineStr">
         <is>
           <t>2026-06-17 11:24:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-07-06 10:37:50</t>
         </is>
       </c>
     </row>
@@ -1788,13 +1805,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34BD3469-273E-43BC-BFDF-29D157941C03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13B3A367-21CF-4C57-874A-4672C0AD2BC9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBFA5618-94B5-4093-B3EF-6CE6388D6FBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2DDDF58-913D-4440-8A62-D4FE4630C5A4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78961B9D-F687-4FE1-8410-2302833B4197}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F51D015F-7582-4008-8491-414793F646F8}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1541,6 +1541,40 @@
       <c r="C70" t="inlineStr">
         <is>
           <t>2026-07-06 10:37:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-07-08 14:59:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-07-08 15:16:30</t>
         </is>
       </c>
     </row>
@@ -1805,13 +1839,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13B3A367-21CF-4C57-874A-4672C0AD2BC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C31F7636-CF02-41E7-841E-F926CA07683C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2DDDF58-913D-4440-8A62-D4FE4630C5A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9341151F-9F06-4135-AFB5-0845FCC864FD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F51D015F-7582-4008-8491-414793F646F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2894612-FBAB-4ECF-B375-3217DD194D15}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1575,6 +1575,40 @@
       <c r="C72" t="inlineStr">
         <is>
           <t>2026-07-08 15:16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-07-09 09:37:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:44:00</t>
         </is>
       </c>
     </row>
@@ -1839,13 +1873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C31F7636-CF02-41E7-841E-F926CA07683C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3080CBE-877D-4EAA-9EA3-3FC4AD65AAE6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9341151F-9F06-4135-AFB5-0845FCC864FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC846CEC-0FB0-432B-87BE-6A951B089D6F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2894612-FBAB-4ECF-B375-3217DD194D15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{104596C0-215E-4D42-A0E2-9C943EC759C3}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1609,6 +1609,74 @@
       <c r="C74" t="inlineStr">
         <is>
           <t>2026-07-13 11:44:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-07-13 14:33:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-07-13 14:37:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:57:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:31:59</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1941,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3080CBE-877D-4EAA-9EA3-3FC4AD65AAE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E0DA420-49BA-4B8D-8B5D-D390707686C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC846CEC-0FB0-432B-87BE-6A951B089D6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CB8AF6B-6CDC-4901-A6DD-BFB1DF5BCE7F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{104596C0-215E-4D42-A0E2-9C943EC759C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48CA3BE9-114E-4F1B-8ED4-F8DF2164CF7B}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1677,6 +1677,40 @@
       <c r="C78" t="inlineStr">
         <is>
           <t>2026-07-13 17:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:49:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:55:47</t>
         </is>
       </c>
     </row>
@@ -1941,13 +1975,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E0DA420-49BA-4B8D-8B5D-D390707686C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B26AFDE9-9090-483E-B732-D05EF01AF7DA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CB8AF6B-6CDC-4901-A6DD-BFB1DF5BCE7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{883316DA-A674-4162-A573-2541DF19E8D8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48CA3BE9-114E-4F1B-8ED4-F8DF2164CF7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0F7780F-821F-4CF8-A0CC-AFCDD78461BD}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1711,6 +1711,23 @@
       <c r="C80" t="inlineStr">
         <is>
           <t>2026-07-14 16:55:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-07-17 10:20:43</t>
         </is>
       </c>
     </row>
@@ -1975,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B26AFDE9-9090-483E-B732-D05EF01AF7DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FF1DC37-7E6A-46D2-84DA-2E0F4B63C274}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{883316DA-A674-4162-A573-2541DF19E8D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EE1F8C9-6195-49A9-BC68-8587A82C248B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0F7780F-821F-4CF8-A0CC-AFCDD78461BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A89BA33C-CF99-44E6-BA00-C441FFC81A15}"/>
 </file>